--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -59,12 +59,11 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,11 +95,6 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -128,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,10 +161,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +553,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-18 ~ 2026-09-29  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-18 ~ 2026-09-29  (최근 5거래일)  ·  캡처 7/7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,865억   ·   현금 35억(0.7%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 15종목  /  매도 16종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,865억   ·   현금 17억(0.4%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 15종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -878,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>997047660</v>
+        <v>2918953800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.85%</t>
+          <t>0.39%→1.00%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>424→477</t>
+          <t>35→88</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2918953800</v>
+        <v>997047660</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.00%</t>
+          <t>1.47%→1.85%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>35→88</t>
+          <t>424→477</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1075,23 +1066,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-866388600</v>
+        <v>-2741392500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.72%→1.95%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2741392500</v>
+        <v>-866388600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>2.72%→1.95%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-646682400</v>
+        <v>-303206400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.52%</t>
+          <t>1.07%→0.96%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1198,46 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-303206400</v>
+        <v>-646682400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.96%</t>
+          <t>0.70%→0.52%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>215659500</v>
+        <v>1004272500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>4.66%→5.10%</t>
+          <t>1.81%→2.03%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1274,23 +1265,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1004272500</v>
+        <v>215659500</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.81%→2.03%</t>
+          <t>4.66%→5.10%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1346,7 +1337,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 76억(2.3%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 3종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 38억(1.2%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1551,7 +1542,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,643억   ·   현금 85억(3.2%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 1종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,643억   ·   현금 42억(1.6%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1740,7 +1731,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,001억   ·   현금 69억(3.4%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,001억   ·   현금 34억(1.7%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -2033,7 +2024,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 300억   ·   현금 2억(0.8%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 9종목  /  매도 11종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 300억   ·   현금 1억(0.4%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 9종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2495,23 +2486,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-51744000</v>
+        <v>-61824000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.26%→2.08%</t>
+          <t>2.80%→2.59%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2523,23 +2514,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-33978000</v>
+        <v>-51744000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.40%</t>
+          <t>2.26%→2.08%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2551,81 +2542,235 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-61824000</v>
+        <v>-33978000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.59%</t>
+          <t>1.52%→1.40%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
-      <c r="J63" s="19" t="n"/>
-      <c r="K63" s="19" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 15억(3.1%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>546612580</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>3.09%→6.23%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>377→464</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-340657375</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>6.23%→4.84%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>443→385</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-26</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-566116490</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>2.63%→0.98%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>47→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,162억      오늘 2026-09-29  vs  5일전 2026-09-18      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A61:K61"/>
     <mergeCell ref="G38:K38"/>
     <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G62:K62"/>
     <mergeCell ref="A37:K37"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A68:K68"/>
     <mergeCell ref="G24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="G47:K47"/>
-    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="G31:K31"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2918953800</v>
+        <v>997047660</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.00%</t>
+          <t>1.47%→1.85%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>35→88</t>
+          <t>424→477</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>997047660</v>
+        <v>2918953800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.85%</t>
+          <t>0.39%→1.00%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>424→477</t>
+          <t>35→88</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1154,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-303206400</v>
+        <v>-646682400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.96%</t>
+          <t>0.70%→0.52%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1198,23 +1198,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-646682400</v>
+        <v>-303206400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.52%</t>
+          <t>1.07%→0.96%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -2421,23 +2421,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>81781000</v>
+        <v>67473000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2465,23 +2465,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>67473000</v>
+        <v>81781000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.42%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 15억(3.1%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 1종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 8억(1.6%)      오늘 2026-09-29  vs  5일전 2026-09-18      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>997047660</v>
+        <v>2918953800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.85%</t>
+          <t>0.39%→1.00%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>424→477</t>
+          <t>35→88</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2918953800</v>
+        <v>997047660</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.00%</t>
+          <t>1.47%→1.85%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>35→88</t>
+          <t>424→477</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1221,23 +1221,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1004272500</v>
+        <v>215659500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.81%→2.03%</t>
+          <t>4.66%→5.10%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1265,23 +1265,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>215659500</v>
+        <v>1004272500</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>4.66%→5.10%</t>
+          <t>1.81%→2.03%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2266,23 +2266,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-32025000</v>
+        <v>-25462500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.58%→2.47%</t>
+          <t>0.18%→0.09%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>31→16</t>
         </is>
       </c>
     </row>
@@ -2310,23 +2310,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-25462500</v>
+        <v>-32025000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.09%</t>
+          <t>2.58%→2.47%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>31→16</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2421,23 +2421,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>67473000</v>
+        <v>81781000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.42%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2465,44 +2465,44 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>81781000</v>
+        <v>67473000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-61824000</v>
+        <v>-33978000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.59%</t>
+          <t>1.52%→1.40%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2514,23 +2514,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-51744000</v>
+        <v>-61824000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.26%→2.08%</t>
+          <t>2.80%→2.59%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2542,23 +2542,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-33978000</v>
+        <v>-51744000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.40%</t>
+          <t>2.26%→2.08%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2918953800</v>
+        <v>997047660</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.00%</t>
+          <t>1.47%→1.85%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>35→88</t>
+          <t>424→477</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>997047660</v>
+        <v>2918953800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.85%</t>
+          <t>0.39%→1.00%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>424→477</t>
+          <t>35→88</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1154,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-646682400</v>
+        <v>-303206400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.52%</t>
+          <t>1.07%→0.96%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -1198,23 +1198,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-303206400</v>
+        <v>-646682400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.96%</t>
+          <t>0.70%→0.52%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -2421,23 +2421,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>81781000</v>
+        <v>67473000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2465,23 +2465,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>67473000</v>
+        <v>81781000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.42%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -1066,23 +1066,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2741392500</v>
+        <v>-866388600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2.72%→1.95%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-866388600</v>
+        <v>-2741392500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.72%→1.95%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -2421,23 +2421,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>67473000</v>
+        <v>81781000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.42%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2465,44 +2465,44 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>81781000</v>
+        <v>67473000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-33978000</v>
+        <v>-51744000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.40%</t>
+          <t>2.26%→2.08%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2514,23 +2514,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-61824000</v>
+        <v>-33978000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.59%</t>
+          <t>1.52%→1.40%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2542,23 +2542,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-51744000</v>
+        <v>-61824000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.26%→2.08%</t>
+          <t>2.80%→2.59%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260929.xlsx
+++ b/reports/pdf_rolling5_20260929.xlsx
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>997047660</v>
+        <v>2918953800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.85%</t>
+          <t>0.39%→1.00%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>424→477</t>
+          <t>35→88</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>53</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2918953800</v>
+        <v>997047660</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.00%</t>
+          <t>1.47%→1.85%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>35→88</t>
+          <t>424→477</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1066,23 +1066,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-866388600</v>
+        <v>-2741392500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.72%→1.95%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2741392500</v>
+        <v>-866388600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>2.72%→1.95%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -2266,23 +2266,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-25462500</v>
+        <v>-32025000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.09%</t>
+          <t>2.58%→2.47%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>31→16</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2310,23 +2310,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-32025000</v>
+        <v>-25462500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.58%→2.47%</t>
+          <t>0.18%→0.09%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>31→16</t>
         </is>
       </c>
     </row>
@@ -2421,23 +2421,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>81781000</v>
+        <v>67473000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2465,23 +2465,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>67473000</v>
+        <v>81781000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.42%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
